--- a/artfynd/A 20274-2026 artfynd.xlsx
+++ b/artfynd/A 20274-2026 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133883868</v>
+        <v>133883918</v>
       </c>
       <c r="B3" t="n">
-        <v>57958</v>
+        <v>91922</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>434276</v>
+        <v>434057</v>
       </c>
       <c r="R3" t="n">
-        <v>7043856</v>
+        <v>7043889</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133883876</v>
+        <v>133883882</v>
       </c>
       <c r="B4" t="n">
         <v>57958</v>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>434136</v>
+        <v>433703</v>
       </c>
       <c r="R4" t="n">
-        <v>7044091</v>
+        <v>7044244</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133883882</v>
+        <v>133883868</v>
       </c>
       <c r="B5" t="n">
         <v>57958</v>
@@ -1016,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>433703</v>
+        <v>434276</v>
       </c>
       <c r="R5" t="n">
-        <v>7044244</v>
+        <v>7043856</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1051,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133883918</v>
+        <v>133883876</v>
       </c>
       <c r="B6" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434057</v>
+        <v>434136</v>
       </c>
       <c r="R6" t="n">
-        <v>7043889</v>
+        <v>7044091</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,6 +1149,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1792,10 +1792,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133883917</v>
+        <v>133883879</v>
       </c>
       <c r="B13" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1803,21 +1803,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1827,10 +1827,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434087</v>
+        <v>433655</v>
       </c>
       <c r="R13" t="n">
-        <v>7044143</v>
+        <v>7044207</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,6 +1863,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1889,10 +1894,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133883879</v>
+        <v>133883917</v>
       </c>
       <c r="B14" t="n">
-        <v>57958</v>
+        <v>91922</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1900,21 +1905,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1924,10 +1929,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>433655</v>
+        <v>434087</v>
       </c>
       <c r="R14" t="n">
-        <v>7044207</v>
+        <v>7044143</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1960,11 +1965,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1991,10 +1991,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133883919</v>
+        <v>133883895</v>
       </c>
       <c r="B15" t="n">
-        <v>79334</v>
+        <v>57958</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2002,21 +2002,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433676</v>
+        <v>434060</v>
       </c>
       <c r="R15" t="n">
-        <v>7044245</v>
+        <v>7044145</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2062,6 +2062,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2088,10 +2093,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133883861</v>
+        <v>133883919</v>
       </c>
       <c r="B16" t="n">
-        <v>91922</v>
+        <v>79334</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2099,21 +2104,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2123,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433574</v>
+        <v>433676</v>
       </c>
       <c r="R16" t="n">
-        <v>7044210</v>
+        <v>7044245</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2185,10 +2190,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133883895</v>
+        <v>133883861</v>
       </c>
       <c r="B17" t="n">
-        <v>57958</v>
+        <v>91926</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2196,21 +2201,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434060</v>
+        <v>433574</v>
       </c>
       <c r="R17" t="n">
-        <v>7044145</v>
+        <v>7044210</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2256,11 +2261,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2287,10 +2287,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133883889</v>
+        <v>133883863</v>
       </c>
       <c r="B18" t="n">
-        <v>57958</v>
+        <v>91926</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2298,21 +2298,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433655</v>
+        <v>434022</v>
       </c>
       <c r="R18" t="n">
-        <v>7044189</v>
+        <v>7044192</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2358,11 +2358,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2491,10 +2486,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133883863</v>
+        <v>133883888</v>
       </c>
       <c r="B20" t="n">
-        <v>91922</v>
+        <v>57958</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2502,21 +2497,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2526,10 +2521,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434022</v>
+        <v>433583</v>
       </c>
       <c r="R20" t="n">
-        <v>7044192</v>
+        <v>7044209</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2562,6 +2557,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2588,7 +2588,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133883888</v>
+        <v>133883889</v>
       </c>
       <c r="B21" t="n">
         <v>57958</v>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433583</v>
+        <v>433655</v>
       </c>
       <c r="R21" t="n">
-        <v>7044209</v>
+        <v>7044189</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3098,7 +3098,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133883862</v>
+        <v>133883915</v>
       </c>
       <c r="B26" t="n">
         <v>91922</v>
@@ -3109,21 +3109,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434042</v>
+        <v>434150</v>
       </c>
       <c r="R26" t="n">
-        <v>7044222</v>
+        <v>7043836</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3195,10 +3195,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133883915</v>
+        <v>133883862</v>
       </c>
       <c r="B27" t="n">
-        <v>91918</v>
+        <v>91926</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3206,21 +3206,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434150</v>
+        <v>434042</v>
       </c>
       <c r="R27" t="n">
-        <v>7043836</v>
+        <v>7044222</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3394,7 +3394,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133883892</v>
+        <v>133883898</v>
       </c>
       <c r="B29" t="n">
         <v>57958</v>
@@ -3429,10 +3429,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434031</v>
+        <v>434117</v>
       </c>
       <c r="R29" t="n">
-        <v>7044214</v>
+        <v>7043922</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3496,7 +3496,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133883898</v>
+        <v>133883892</v>
       </c>
       <c r="B30" t="n">
         <v>57958</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434117</v>
+        <v>434031</v>
       </c>
       <c r="R30" t="n">
-        <v>7043922</v>
+        <v>7044214</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3904,10 +3904,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133883864</v>
+        <v>133883874</v>
       </c>
       <c r="B34" t="n">
-        <v>91922</v>
+        <v>57958</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3915,21 +3915,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3939,10 +3939,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>434028</v>
+        <v>434132</v>
       </c>
       <c r="R34" t="n">
-        <v>7044149</v>
+        <v>7044056</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3975,6 +3975,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4001,10 +4006,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133883874</v>
+        <v>133883864</v>
       </c>
       <c r="B35" t="n">
-        <v>57958</v>
+        <v>91926</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4012,21 +4017,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4036,10 +4041,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434132</v>
+        <v>434028</v>
       </c>
       <c r="R35" t="n">
-        <v>7044056</v>
+        <v>7044149</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4072,11 +4077,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 20274-2026 artfynd.xlsx
+++ b/artfynd/A 20274-2026 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>133883918</v>
       </c>
       <c r="B3" t="n">
-        <v>91922</v>
+        <v>91924</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133883879</v>
+        <v>133883917</v>
       </c>
       <c r="B13" t="n">
-        <v>57958</v>
+        <v>91924</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1803,21 +1803,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1827,10 +1827,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>433655</v>
+        <v>434087</v>
       </c>
       <c r="R13" t="n">
-        <v>7044207</v>
+        <v>7044143</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,11 +1863,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1894,10 +1889,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133883917</v>
+        <v>133883879</v>
       </c>
       <c r="B14" t="n">
-        <v>91922</v>
+        <v>57958</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1905,21 +1900,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1929,10 +1924,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>434087</v>
+        <v>433655</v>
       </c>
       <c r="R14" t="n">
-        <v>7044143</v>
+        <v>7044207</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1965,6 +1960,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1991,10 +1991,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133883895</v>
+        <v>133883919</v>
       </c>
       <c r="B15" t="n">
-        <v>57958</v>
+        <v>79334</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2002,21 +2002,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434060</v>
+        <v>433676</v>
       </c>
       <c r="R15" t="n">
-        <v>7044145</v>
+        <v>7044245</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2062,11 +2062,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2093,10 +2088,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133883919</v>
+        <v>133883861</v>
       </c>
       <c r="B16" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2104,21 +2099,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2128,10 +2123,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433676</v>
+        <v>433574</v>
       </c>
       <c r="R16" t="n">
-        <v>7044245</v>
+        <v>7044210</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2190,10 +2185,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133883861</v>
+        <v>133883895</v>
       </c>
       <c r="B17" t="n">
-        <v>91926</v>
+        <v>57958</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2201,21 +2196,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2225,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433574</v>
+        <v>434060</v>
       </c>
       <c r="R17" t="n">
-        <v>7044210</v>
+        <v>7044145</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2261,6 +2256,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2290,7 +2290,7 @@
         <v>133883863</v>
       </c>
       <c r="B18" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>133883915</v>
       </c>
       <c r="B26" t="n">
-        <v>91922</v>
+        <v>91924</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>133883862</v>
       </c>
       <c r="B27" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3904,10 +3904,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133883874</v>
+        <v>133883864</v>
       </c>
       <c r="B34" t="n">
-        <v>57958</v>
+        <v>91928</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3915,21 +3915,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3939,10 +3939,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>434132</v>
+        <v>434028</v>
       </c>
       <c r="R34" t="n">
-        <v>7044056</v>
+        <v>7044149</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3975,11 +3975,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4006,10 +4001,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133883864</v>
+        <v>133883874</v>
       </c>
       <c r="B35" t="n">
-        <v>91926</v>
+        <v>57958</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4017,21 +4012,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4041,10 +4036,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434028</v>
+        <v>434132</v>
       </c>
       <c r="R35" t="n">
-        <v>7044149</v>
+        <v>7044056</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4077,6 +4072,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 20274-2026 artfynd.xlsx
+++ b/artfynd/A 20274-2026 artfynd.xlsx
@@ -2287,10 +2287,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133883863</v>
+        <v>133883881</v>
       </c>
       <c r="B18" t="n">
-        <v>91928</v>
+        <v>57958</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2298,21 +2298,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>434022</v>
+        <v>433698</v>
       </c>
       <c r="R18" t="n">
-        <v>7044192</v>
+        <v>7044230</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2358,6 +2358,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2384,7 +2389,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133883881</v>
+        <v>133883888</v>
       </c>
       <c r="B19" t="n">
         <v>57958</v>
@@ -2419,10 +2424,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433698</v>
+        <v>433583</v>
       </c>
       <c r="R19" t="n">
-        <v>7044230</v>
+        <v>7044209</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2486,7 +2491,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133883888</v>
+        <v>133883889</v>
       </c>
       <c r="B20" t="n">
         <v>57958</v>
@@ -2521,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433583</v>
+        <v>433655</v>
       </c>
       <c r="R20" t="n">
-        <v>7044209</v>
+        <v>7044189</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2561,7 +2566,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2588,10 +2593,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133883889</v>
+        <v>133883863</v>
       </c>
       <c r="B21" t="n">
-        <v>57958</v>
+        <v>91928</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2599,21 +2604,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2623,10 +2628,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433655</v>
+        <v>434022</v>
       </c>
       <c r="R21" t="n">
-        <v>7044189</v>
+        <v>7044192</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2659,11 +2664,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 20274-2026 artfynd.xlsx
+++ b/artfynd/A 20274-2026 artfynd.xlsx
@@ -3098,10 +3098,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133883915</v>
+        <v>133883899</v>
       </c>
       <c r="B26" t="n">
-        <v>91924</v>
+        <v>57958</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3109,21 +3109,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434150</v>
+        <v>433968</v>
       </c>
       <c r="R26" t="n">
-        <v>7043836</v>
+        <v>7043952</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3169,6 +3169,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3195,10 +3200,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133883862</v>
+        <v>133883915</v>
       </c>
       <c r="B27" t="n">
-        <v>91928</v>
+        <v>91924</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3206,21 +3211,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3230,10 +3235,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434042</v>
+        <v>434150</v>
       </c>
       <c r="R27" t="n">
-        <v>7044222</v>
+        <v>7043836</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3292,10 +3297,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133883899</v>
+        <v>133883862</v>
       </c>
       <c r="B28" t="n">
-        <v>57958</v>
+        <v>91928</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3303,21 +3308,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3327,10 +3332,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>433968</v>
+        <v>434042</v>
       </c>
       <c r="R28" t="n">
-        <v>7043952</v>
+        <v>7044222</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3363,11 +3368,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 20274-2026 artfynd.xlsx
+++ b/artfynd/A 20274-2026 artfynd.xlsx
@@ -2287,10 +2287,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133883881</v>
+        <v>133883863</v>
       </c>
       <c r="B18" t="n">
-        <v>57958</v>
+        <v>91928</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2298,21 +2298,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433698</v>
+        <v>434022</v>
       </c>
       <c r="R18" t="n">
-        <v>7044230</v>
+        <v>7044192</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2358,11 +2358,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2389,7 +2384,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133883888</v>
+        <v>133883881</v>
       </c>
       <c r="B19" t="n">
         <v>57958</v>
@@ -2424,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433583</v>
+        <v>433698</v>
       </c>
       <c r="R19" t="n">
-        <v>7044209</v>
+        <v>7044230</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2491,7 +2486,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133883889</v>
+        <v>133883888</v>
       </c>
       <c r="B20" t="n">
         <v>57958</v>
@@ -2526,10 +2521,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433655</v>
+        <v>433583</v>
       </c>
       <c r="R20" t="n">
-        <v>7044189</v>
+        <v>7044209</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2566,7 +2561,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2593,10 +2588,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133883863</v>
+        <v>133883889</v>
       </c>
       <c r="B21" t="n">
-        <v>91928</v>
+        <v>57958</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2604,21 +2599,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2628,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434022</v>
+        <v>433655</v>
       </c>
       <c r="R21" t="n">
-        <v>7044192</v>
+        <v>7044189</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2664,6 +2659,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3098,10 +3098,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133883899</v>
+        <v>133883915</v>
       </c>
       <c r="B26" t="n">
-        <v>57958</v>
+        <v>91924</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3109,21 +3109,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>433968</v>
+        <v>434150</v>
       </c>
       <c r="R26" t="n">
-        <v>7043952</v>
+        <v>7043836</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3169,11 +3169,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3200,10 +3195,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133883915</v>
+        <v>133883862</v>
       </c>
       <c r="B27" t="n">
-        <v>91924</v>
+        <v>91928</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3211,21 +3206,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3235,10 +3230,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434150</v>
+        <v>434042</v>
       </c>
       <c r="R27" t="n">
-        <v>7043836</v>
+        <v>7044222</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3297,10 +3292,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133883862</v>
+        <v>133883899</v>
       </c>
       <c r="B28" t="n">
-        <v>91928</v>
+        <v>57958</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3308,21 +3303,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3332,10 +3327,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434042</v>
+        <v>433968</v>
       </c>
       <c r="R28" t="n">
-        <v>7044222</v>
+        <v>7043952</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3368,6 +3363,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 20274-2026 artfynd.xlsx
+++ b/artfynd/A 20274-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133883883</v>
       </c>
       <c r="B2" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>133883918</v>
       </c>
       <c r="B3" t="n">
-        <v>91924</v>
+        <v>91943</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>133883882</v>
       </c>
       <c r="B4" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>133883868</v>
       </c>
       <c r="B5" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>133883876</v>
       </c>
       <c r="B6" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>133883880</v>
       </c>
       <c r="B7" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>133883866</v>
       </c>
       <c r="B8" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>133883875</v>
       </c>
       <c r="B9" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>133883894</v>
       </c>
       <c r="B10" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>133883891</v>
       </c>
       <c r="B11" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>133883877</v>
       </c>
       <c r="B12" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>133883917</v>
       </c>
       <c r="B13" t="n">
-        <v>91924</v>
+        <v>91943</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>133883879</v>
       </c>
       <c r="B14" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,10 +1991,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133883919</v>
+        <v>133883895</v>
       </c>
       <c r="B15" t="n">
-        <v>79334</v>
+        <v>57965</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2002,21 +2002,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433676</v>
+        <v>434060</v>
       </c>
       <c r="R15" t="n">
-        <v>7044245</v>
+        <v>7044145</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2062,6 +2062,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2088,10 +2093,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133883861</v>
+        <v>133883919</v>
       </c>
       <c r="B16" t="n">
-        <v>91928</v>
+        <v>79348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2099,21 +2104,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2123,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433574</v>
+        <v>433676</v>
       </c>
       <c r="R16" t="n">
-        <v>7044210</v>
+        <v>7044245</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2185,10 +2190,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133883895</v>
+        <v>133883861</v>
       </c>
       <c r="B17" t="n">
-        <v>57958</v>
+        <v>91947</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2196,21 +2201,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434060</v>
+        <v>433574</v>
       </c>
       <c r="R17" t="n">
-        <v>7044145</v>
+        <v>7044210</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2256,11 +2261,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2290,7 +2290,7 @@
         <v>133883863</v>
       </c>
       <c r="B18" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>133883881</v>
       </c>
       <c r="B19" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>133883888</v>
       </c>
       <c r="B20" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>133883889</v>
       </c>
       <c r="B21" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>133883884</v>
       </c>
       <c r="B22" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>133883890</v>
       </c>
       <c r="B23" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>133883885</v>
       </c>
       <c r="B24" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>133883887</v>
       </c>
       <c r="B25" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>133883915</v>
       </c>
       <c r="B26" t="n">
-        <v>91924</v>
+        <v>91943</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3195,10 +3195,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133883862</v>
+        <v>133883899</v>
       </c>
       <c r="B27" t="n">
-        <v>91928</v>
+        <v>57965</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3206,21 +3206,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434042</v>
+        <v>433968</v>
       </c>
       <c r="R27" t="n">
-        <v>7044222</v>
+        <v>7043952</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3266,6 +3266,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3292,10 +3297,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133883899</v>
+        <v>133883862</v>
       </c>
       <c r="B28" t="n">
-        <v>57958</v>
+        <v>91947</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3303,21 +3308,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3327,10 +3332,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>433968</v>
+        <v>434042</v>
       </c>
       <c r="R28" t="n">
-        <v>7043952</v>
+        <v>7044222</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3363,11 +3368,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3397,7 +3397,7 @@
         <v>133883898</v>
       </c>
       <c r="B29" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>133883892</v>
       </c>
       <c r="B30" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>133883893</v>
       </c>
       <c r="B31" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>133883878</v>
       </c>
       <c r="B32" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>133883897</v>
       </c>
       <c r="B33" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>133883864</v>
       </c>
       <c r="B34" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>133883874</v>
       </c>
       <c r="B35" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>133883886</v>
       </c>
       <c r="B36" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 20274-2026 artfynd.xlsx
+++ b/artfynd/A 20274-2026 artfynd.xlsx
@@ -1991,10 +1991,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133883895</v>
+        <v>133883919</v>
       </c>
       <c r="B15" t="n">
-        <v>57965</v>
+        <v>79348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2002,21 +2002,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434060</v>
+        <v>433676</v>
       </c>
       <c r="R15" t="n">
-        <v>7044145</v>
+        <v>7044245</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2062,11 +2062,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2093,10 +2088,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133883919</v>
+        <v>133883861</v>
       </c>
       <c r="B16" t="n">
-        <v>79348</v>
+        <v>91947</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2104,21 +2099,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2128,10 +2123,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433676</v>
+        <v>433574</v>
       </c>
       <c r="R16" t="n">
-        <v>7044245</v>
+        <v>7044210</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2190,10 +2185,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133883861</v>
+        <v>133883895</v>
       </c>
       <c r="B17" t="n">
-        <v>91947</v>
+        <v>57965</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2201,21 +2196,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2225,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433574</v>
+        <v>434060</v>
       </c>
       <c r="R17" t="n">
-        <v>7044210</v>
+        <v>7044145</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2261,6 +2256,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3098,10 +3098,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133883915</v>
+        <v>133883899</v>
       </c>
       <c r="B26" t="n">
-        <v>91943</v>
+        <v>57965</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3109,21 +3109,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434150</v>
+        <v>433968</v>
       </c>
       <c r="R26" t="n">
-        <v>7043836</v>
+        <v>7043952</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3169,6 +3169,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3195,10 +3200,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133883899</v>
+        <v>133883862</v>
       </c>
       <c r="B27" t="n">
-        <v>57965</v>
+        <v>91947</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3206,21 +3211,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3230,10 +3235,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>433968</v>
+        <v>434042</v>
       </c>
       <c r="R27" t="n">
-        <v>7043952</v>
+        <v>7044222</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3266,11 +3271,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3297,10 +3297,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133883862</v>
+        <v>133883915</v>
       </c>
       <c r="B28" t="n">
-        <v>91947</v>
+        <v>91943</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3308,21 +3308,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434042</v>
+        <v>434150</v>
       </c>
       <c r="R28" t="n">
-        <v>7044222</v>
+        <v>7043836</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3904,10 +3904,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133883864</v>
+        <v>133883874</v>
       </c>
       <c r="B34" t="n">
-        <v>91947</v>
+        <v>57965</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3915,21 +3915,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3939,10 +3939,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>434028</v>
+        <v>434132</v>
       </c>
       <c r="R34" t="n">
-        <v>7044149</v>
+        <v>7044056</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3975,6 +3975,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4001,10 +4006,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133883874</v>
+        <v>133883864</v>
       </c>
       <c r="B35" t="n">
-        <v>57965</v>
+        <v>91947</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4012,21 +4017,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4036,10 +4041,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434132</v>
+        <v>434028</v>
       </c>
       <c r="R35" t="n">
-        <v>7044056</v>
+        <v>7044149</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4072,11 +4077,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 20274-2026 artfynd.xlsx
+++ b/artfynd/A 20274-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133883883</v>
       </c>
       <c r="B2" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>133883918</v>
       </c>
       <c r="B3" t="n">
-        <v>91943</v>
+        <v>91953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>133883882</v>
       </c>
       <c r="B4" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>133883868</v>
       </c>
       <c r="B5" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>133883876</v>
       </c>
       <c r="B6" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>133883880</v>
       </c>
       <c r="B7" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>133883866</v>
       </c>
       <c r="B8" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>133883875</v>
       </c>
       <c r="B9" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>133883894</v>
       </c>
       <c r="B10" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>133883891</v>
       </c>
       <c r="B11" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>133883877</v>
       </c>
       <c r="B12" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>133883917</v>
       </c>
       <c r="B13" t="n">
-        <v>91943</v>
+        <v>91953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>133883879</v>
       </c>
       <c r="B14" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,10 +1991,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133883919</v>
+        <v>133883895</v>
       </c>
       <c r="B15" t="n">
-        <v>79348</v>
+        <v>57975</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2002,21 +2002,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433676</v>
+        <v>434060</v>
       </c>
       <c r="R15" t="n">
-        <v>7044245</v>
+        <v>7044145</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2062,6 +2062,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2088,10 +2093,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133883861</v>
+        <v>133883919</v>
       </c>
       <c r="B16" t="n">
-        <v>91947</v>
+        <v>79358</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2099,21 +2104,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2123,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433574</v>
+        <v>433676</v>
       </c>
       <c r="R16" t="n">
-        <v>7044210</v>
+        <v>7044245</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2185,10 +2190,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133883895</v>
+        <v>133883861</v>
       </c>
       <c r="B17" t="n">
-        <v>57965</v>
+        <v>91957</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2196,21 +2201,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434060</v>
+        <v>433574</v>
       </c>
       <c r="R17" t="n">
-        <v>7044145</v>
+        <v>7044210</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2256,11 +2261,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2290,7 +2290,7 @@
         <v>133883863</v>
       </c>
       <c r="B18" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>133883881</v>
       </c>
       <c r="B19" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>133883888</v>
       </c>
       <c r="B20" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>133883889</v>
       </c>
       <c r="B21" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>133883884</v>
       </c>
       <c r="B22" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>133883890</v>
       </c>
       <c r="B23" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>133883885</v>
       </c>
       <c r="B24" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>133883887</v>
       </c>
       <c r="B25" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3098,10 +3098,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133883899</v>
+        <v>133883915</v>
       </c>
       <c r="B26" t="n">
-        <v>57965</v>
+        <v>91953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3109,21 +3109,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>433968</v>
+        <v>434150</v>
       </c>
       <c r="R26" t="n">
-        <v>7043952</v>
+        <v>7043836</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3169,11 +3169,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3200,10 +3195,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133883862</v>
+        <v>133883899</v>
       </c>
       <c r="B27" t="n">
-        <v>91947</v>
+        <v>57975</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3211,21 +3206,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3235,10 +3230,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434042</v>
+        <v>433968</v>
       </c>
       <c r="R27" t="n">
-        <v>7044222</v>
+        <v>7043952</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3271,6 +3266,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3297,10 +3297,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133883915</v>
+        <v>133883862</v>
       </c>
       <c r="B28" t="n">
-        <v>91943</v>
+        <v>91957</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3308,21 +3308,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434150</v>
+        <v>434042</v>
       </c>
       <c r="R28" t="n">
-        <v>7043836</v>
+        <v>7044222</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3397,7 +3397,7 @@
         <v>133883898</v>
       </c>
       <c r="B29" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>133883892</v>
       </c>
       <c r="B30" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>133883893</v>
       </c>
       <c r="B31" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>133883878</v>
       </c>
       <c r="B32" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>133883897</v>
       </c>
       <c r="B33" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3904,10 +3904,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133883874</v>
+        <v>133883864</v>
       </c>
       <c r="B34" t="n">
-        <v>57965</v>
+        <v>91957</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3915,21 +3915,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3939,10 +3939,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>434132</v>
+        <v>434028</v>
       </c>
       <c r="R34" t="n">
-        <v>7044056</v>
+        <v>7044149</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3975,11 +3975,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4006,10 +4001,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133883864</v>
+        <v>133883874</v>
       </c>
       <c r="B35" t="n">
-        <v>91947</v>
+        <v>57975</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4017,21 +4012,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4041,10 +4036,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434028</v>
+        <v>434132</v>
       </c>
       <c r="R35" t="n">
-        <v>7044149</v>
+        <v>7044056</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4077,6 +4072,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4106,7 +4106,7 @@
         <v>133883886</v>
       </c>
       <c r="B36" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 20274-2026 artfynd.xlsx
+++ b/artfynd/A 20274-2026 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133883918</v>
+        <v>133883882</v>
       </c>
       <c r="B3" t="n">
-        <v>91953</v>
+        <v>57975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>434057</v>
+        <v>433703</v>
       </c>
       <c r="R3" t="n">
-        <v>7043889</v>
+        <v>7044244</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133883882</v>
+        <v>133883868</v>
       </c>
       <c r="B4" t="n">
         <v>57975</v>
@@ -909,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433703</v>
+        <v>434276</v>
       </c>
       <c r="R4" t="n">
-        <v>7044244</v>
+        <v>7043856</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133883868</v>
+        <v>133883876</v>
       </c>
       <c r="B5" t="n">
         <v>57975</v>
@@ -1011,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>434276</v>
+        <v>434136</v>
       </c>
       <c r="R5" t="n">
-        <v>7043856</v>
+        <v>7044091</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,7 +1056,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133883876</v>
+        <v>133883918</v>
       </c>
       <c r="B6" t="n">
-        <v>57975</v>
+        <v>91953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434136</v>
+        <v>434057</v>
       </c>
       <c r="R6" t="n">
-        <v>7044091</v>
+        <v>7043889</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,11 +1154,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2287,10 +2287,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133883863</v>
+        <v>133883881</v>
       </c>
       <c r="B18" t="n">
-        <v>91957</v>
+        <v>57975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2298,21 +2298,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>434022</v>
+        <v>433698</v>
       </c>
       <c r="R18" t="n">
-        <v>7044192</v>
+        <v>7044230</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2358,6 +2358,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2384,7 +2389,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133883881</v>
+        <v>133883888</v>
       </c>
       <c r="B19" t="n">
         <v>57975</v>
@@ -2419,10 +2424,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433698</v>
+        <v>433583</v>
       </c>
       <c r="R19" t="n">
-        <v>7044230</v>
+        <v>7044209</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2486,7 +2491,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133883888</v>
+        <v>133883889</v>
       </c>
       <c r="B20" t="n">
         <v>57975</v>
@@ -2521,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433583</v>
+        <v>433655</v>
       </c>
       <c r="R20" t="n">
-        <v>7044209</v>
+        <v>7044189</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2561,7 +2566,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2588,10 +2593,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133883889</v>
+        <v>133883863</v>
       </c>
       <c r="B21" t="n">
-        <v>57975</v>
+        <v>91957</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2599,21 +2604,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2623,10 +2628,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433655</v>
+        <v>434022</v>
       </c>
       <c r="R21" t="n">
-        <v>7044189</v>
+        <v>7044192</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2659,11 +2664,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3098,10 +3098,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133883915</v>
+        <v>133883899</v>
       </c>
       <c r="B26" t="n">
-        <v>91953</v>
+        <v>57975</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3109,21 +3109,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434150</v>
+        <v>433968</v>
       </c>
       <c r="R26" t="n">
-        <v>7043836</v>
+        <v>7043952</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3169,6 +3169,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3195,10 +3200,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133883899</v>
+        <v>133883862</v>
       </c>
       <c r="B27" t="n">
-        <v>57975</v>
+        <v>91957</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3206,21 +3211,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3230,10 +3235,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>433968</v>
+        <v>434042</v>
       </c>
       <c r="R27" t="n">
-        <v>7043952</v>
+        <v>7044222</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3266,11 +3271,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3297,10 +3297,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133883862</v>
+        <v>133883915</v>
       </c>
       <c r="B28" t="n">
-        <v>91957</v>
+        <v>91953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3308,21 +3308,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434042</v>
+        <v>434150</v>
       </c>
       <c r="R28" t="n">
-        <v>7044222</v>
+        <v>7043836</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3904,10 +3904,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133883864</v>
+        <v>133883874</v>
       </c>
       <c r="B34" t="n">
-        <v>91957</v>
+        <v>57975</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3915,21 +3915,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3939,10 +3939,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>434028</v>
+        <v>434132</v>
       </c>
       <c r="R34" t="n">
-        <v>7044149</v>
+        <v>7044056</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3975,6 +3975,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4001,10 +4006,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133883874</v>
+        <v>133883864</v>
       </c>
       <c r="B35" t="n">
-        <v>57975</v>
+        <v>91957</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4012,21 +4017,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4036,10 +4041,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434132</v>
+        <v>434028</v>
       </c>
       <c r="R35" t="n">
-        <v>7044056</v>
+        <v>7044149</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4072,11 +4077,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 20274-2026 artfynd.xlsx
+++ b/artfynd/A 20274-2026 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133883882</v>
+        <v>133883918</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>91953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>433703</v>
+        <v>434057</v>
       </c>
       <c r="R3" t="n">
-        <v>7044244</v>
+        <v>7043889</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133883868</v>
+        <v>133883882</v>
       </c>
       <c r="B4" t="n">
         <v>57975</v>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>434276</v>
+        <v>433703</v>
       </c>
       <c r="R4" t="n">
-        <v>7043856</v>
+        <v>7044244</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +949,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133883876</v>
+        <v>133883868</v>
       </c>
       <c r="B5" t="n">
         <v>57975</v>
@@ -1016,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>434136</v>
+        <v>434276</v>
       </c>
       <c r="R5" t="n">
-        <v>7044091</v>
+        <v>7043856</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1051,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133883918</v>
+        <v>133883876</v>
       </c>
       <c r="B6" t="n">
-        <v>91953</v>
+        <v>57975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434057</v>
+        <v>434136</v>
       </c>
       <c r="R6" t="n">
-        <v>7043889</v>
+        <v>7044091</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,6 +1149,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1486,7 +1486,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133883894</v>
+        <v>133883891</v>
       </c>
       <c r="B10" t="n">
         <v>57975</v>
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434028</v>
+        <v>434033</v>
       </c>
       <c r="R10" t="n">
-        <v>7044145</v>
+        <v>7044220</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1588,7 +1588,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133883891</v>
+        <v>133883894</v>
       </c>
       <c r="B11" t="n">
         <v>57975</v>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434033</v>
+        <v>434028</v>
       </c>
       <c r="R11" t="n">
-        <v>7044220</v>
+        <v>7044145</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2287,10 +2287,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133883881</v>
+        <v>133883863</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>91957</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2298,21 +2298,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433698</v>
+        <v>434022</v>
       </c>
       <c r="R18" t="n">
-        <v>7044230</v>
+        <v>7044192</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2358,11 +2358,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2389,7 +2384,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133883888</v>
+        <v>133883881</v>
       </c>
       <c r="B19" t="n">
         <v>57975</v>
@@ -2424,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433583</v>
+        <v>433698</v>
       </c>
       <c r="R19" t="n">
-        <v>7044209</v>
+        <v>7044230</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2491,7 +2486,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133883889</v>
+        <v>133883888</v>
       </c>
       <c r="B20" t="n">
         <v>57975</v>
@@ -2526,10 +2521,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433655</v>
+        <v>433583</v>
       </c>
       <c r="R20" t="n">
-        <v>7044189</v>
+        <v>7044209</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2566,7 +2561,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2593,10 +2588,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133883863</v>
+        <v>133883889</v>
       </c>
       <c r="B21" t="n">
-        <v>91957</v>
+        <v>57975</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2604,21 +2599,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2628,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434022</v>
+        <v>433655</v>
       </c>
       <c r="R21" t="n">
-        <v>7044192</v>
+        <v>7044189</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2664,6 +2659,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3098,10 +3098,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133883899</v>
+        <v>133883915</v>
       </c>
       <c r="B26" t="n">
-        <v>57975</v>
+        <v>91953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3109,21 +3109,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>433968</v>
+        <v>434150</v>
       </c>
       <c r="R26" t="n">
-        <v>7043952</v>
+        <v>7043836</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3169,11 +3169,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3297,10 +3292,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133883915</v>
+        <v>133883899</v>
       </c>
       <c r="B28" t="n">
-        <v>91953</v>
+        <v>57975</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3308,21 +3303,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3332,10 +3327,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434150</v>
+        <v>433968</v>
       </c>
       <c r="R28" t="n">
-        <v>7043836</v>
+        <v>7043952</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3368,6 +3363,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3598,7 +3598,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133883893</v>
+        <v>133883878</v>
       </c>
       <c r="B31" t="n">
         <v>57975</v>
@@ -3633,10 +3633,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434025</v>
+        <v>433976</v>
       </c>
       <c r="R31" t="n">
-        <v>7044203</v>
+        <v>7044282</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3700,7 +3700,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133883878</v>
+        <v>133883893</v>
       </c>
       <c r="B32" t="n">
         <v>57975</v>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>433976</v>
+        <v>434025</v>
       </c>
       <c r="R32" t="n">
-        <v>7044282</v>
+        <v>7044203</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3904,10 +3904,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133883874</v>
+        <v>133883864</v>
       </c>
       <c r="B34" t="n">
-        <v>57975</v>
+        <v>91957</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3915,21 +3915,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3939,10 +3939,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>434132</v>
+        <v>434028</v>
       </c>
       <c r="R34" t="n">
-        <v>7044056</v>
+        <v>7044149</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3975,11 +3975,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4006,10 +4001,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133883864</v>
+        <v>133883874</v>
       </c>
       <c r="B35" t="n">
-        <v>91957</v>
+        <v>57975</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4017,21 +4012,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4041,10 +4036,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434028</v>
+        <v>434132</v>
       </c>
       <c r="R35" t="n">
-        <v>7044149</v>
+        <v>7044056</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4077,6 +4072,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 20274-2026 artfynd.xlsx
+++ b/artfynd/A 20274-2026 artfynd.xlsx
@@ -1991,10 +1991,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133883895</v>
+        <v>133883919</v>
       </c>
       <c r="B15" t="n">
-        <v>57975</v>
+        <v>79358</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2002,21 +2002,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434060</v>
+        <v>433676</v>
       </c>
       <c r="R15" t="n">
-        <v>7044145</v>
+        <v>7044245</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2062,11 +2062,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2093,10 +2088,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133883919</v>
+        <v>133883861</v>
       </c>
       <c r="B16" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2104,21 +2099,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2128,10 +2123,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433676</v>
+        <v>433574</v>
       </c>
       <c r="R16" t="n">
-        <v>7044245</v>
+        <v>7044210</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2190,10 +2185,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133883861</v>
+        <v>133883895</v>
       </c>
       <c r="B17" t="n">
-        <v>91957</v>
+        <v>57975</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2201,21 +2196,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2225,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433574</v>
+        <v>434060</v>
       </c>
       <c r="R17" t="n">
-        <v>7044210</v>
+        <v>7044145</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2261,6 +2256,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
